--- a/AAII_Financials/Quarterly/MASK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MASK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="92">
   <si>
     <t>MASK</t>
   </si>
@@ -749,10 +749,10 @@
         <v>10</v>
       </c>
       <c r="H8" s="3">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="I8" s="3">
-        <v>1600</v>
+        <v>900</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>10</v>
@@ -796,10 +796,10 @@
         <v>10</v>
       </c>
       <c r="H9" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="I9" s="3">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>10</v>
@@ -843,10 +843,10 @@
         <v>10</v>
       </c>
       <c r="H10" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="I10" s="3">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>10</v>
@@ -908,11 +908,11 @@
       <c r="G12" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="3">
-        <v>100</v>
-      </c>
-      <c r="I12" s="3">
-        <v>100</v>
+      <c r="H12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>10</v>
@@ -1113,10 +1113,10 @@
         <v>10</v>
       </c>
       <c r="H17" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="I17" s="3">
-        <v>900</v>
+        <v>400</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>10</v>
@@ -1160,10 +1160,10 @@
         <v>10</v>
       </c>
       <c r="H18" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I18" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>10</v>
@@ -1273,10 +1273,10 @@
         <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I21" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
@@ -1367,10 +1367,10 @@
         <v>10</v>
       </c>
       <c r="H23" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="I23" s="3">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>10</v>
@@ -1508,10 +1508,10 @@
         <v>10</v>
       </c>
       <c r="H26" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="I26" s="3">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>10</v>
@@ -1649,10 +1649,10 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J29" s="3">
         <v>0</v>
@@ -2103,10 +2103,10 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="E42" s="3">
-        <v>4400</v>
+        <v>2500</v>
       </c>
       <c r="F42" s="3">
         <v>2400</v>
@@ -2150,10 +2150,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4500</v>
+        <v>6300</v>
       </c>
       <c r="E43" s="3">
-        <v>4500</v>
+        <v>6300</v>
       </c>
       <c r="F43" s="3">
         <v>4300</v>
@@ -2573,10 +2573,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>3300</v>
+        <v>1600</v>
       </c>
       <c r="E52" s="3">
-        <v>3300</v>
+        <v>1600</v>
       </c>
       <c r="F52" s="3">
         <v>1500</v>
@@ -2799,10 +2799,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F58" s="3">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="E59" s="3">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="F59" s="3">
         <v>2700</v>
@@ -3828,11 +3828,11 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>10</v>
